--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Scommesse" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Riepilogo" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Note" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t xml:space="preserve">Data</t>
   </si>
@@ -123,6 +124,27 @@
   </si>
   <si>
     <t xml:space="preserve">ROI complessivo (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perché tengo questo diario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrare ogni giocata mi obbliga a essere onesto con me stesso. Senza numeri scritti si ricordano solo le vincite, e il quadro che ne esce non ha niente a che vedere con la realtà. Qui c'è tutto, comprese le perdite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiefs – Bills, letta male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avevo puntato sull'over convinto dal ritmo delle ultime uscite, ignorando il meteo previsto e la difesa in ripresa di Buffalo. Un dato preso da solo, fuori contesto, non vale granché.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le note più recenti vanno in cima. La data si scrive AAAA-MM-GG.</t>
   </si>
 </sst>
 </file>
@@ -137,7 +159,7 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,6 +240,20 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -282,11 +318,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -311,56 +351,80 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -420,7 +484,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -618,615 +682,615 @@
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>1.85</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="6" t="n">
         <f aca="false">IF(G2="Vinta",(E2*F2)-F2,IF(G2="Persa",-F2,0))</f>
         <v>85</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="7" t="n">
         <f aca="false">IFERROR(H2/F2,0)</f>
         <v>0.85</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <f aca="false">IF(G3="Vinta",(E3*F3)-F3,IF(G3="Persa",-F3,0))</f>
         <v>-150</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <f aca="false">IFERROR(H3/F3,0)</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <f aca="false">IF(G4="Vinta",(E4*F4)-F4,IF(G4="Persa",-F4,0))</f>
         <v>80</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <f aca="false">IFERROR(H4/F4,0)</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="10" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="11" t="n">
         <f aca="false">IF(G5="Vinta",(E5*F5)-F5,IF(G5="Persa",-F5,0))</f>
         <v>0</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="12" t="n">
         <f aca="false">IFERROR(H5/F5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="10" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="11" t="n">
         <f aca="false">IF(G6="Vinta",(E6*F6)-F6,IF(G6="Persa",-F6,0))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="12" t="n">
         <f aca="false">IFERROR(H6/F6,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="10" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="11" t="n">
         <f aca="false">IF(G7="Vinta",(E7*F7)-F7,IF(G7="Persa",-F7,0))</f>
         <v>0</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="12" t="n">
         <f aca="false">IFERROR(H7/F7,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="10" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="11" t="n">
         <f aca="false">IF(G8="Vinta",(E8*F8)-F8,IF(G8="Persa",-F8,0))</f>
         <v>0</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="12" t="n">
         <f aca="false">IFERROR(H8/F8,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="10" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="11" t="n">
         <f aca="false">IF(G9="Vinta",(E9*F9)-F9,IF(G9="Persa",-F9,0))</f>
         <v>0</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="12" t="n">
         <f aca="false">IFERROR(H9/F9,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="10" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="11" t="n">
         <f aca="false">IF(G10="Vinta",(E10*F10)-F10,IF(G10="Persa",-F10,0))</f>
         <v>0</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="12" t="n">
         <f aca="false">IFERROR(H10/F10,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="10" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="11" t="n">
         <f aca="false">IF(G11="Vinta",(E11*F11)-F11,IF(G11="Persa",-F11,0))</f>
         <v>0</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="12" t="n">
         <f aca="false">IFERROR(H11/F11,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="10" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="11" t="n">
         <f aca="false">IF(G12="Vinta",(E12*F12)-F12,IF(G12="Persa",-F12,0))</f>
         <v>0</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="12" t="n">
         <f aca="false">IFERROR(H12/F12,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="10" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="11" t="n">
         <f aca="false">IF(G13="Vinta",(E13*F13)-F13,IF(G13="Persa",-F13,0))</f>
         <v>0</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="I13" s="12" t="n">
         <f aca="false">IFERROR(H13/F13,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="10" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="11" t="n">
         <f aca="false">IF(G14="Vinta",(E14*F14)-F14,IF(G14="Persa",-F14,0))</f>
         <v>0</v>
       </c>
-      <c r="I14" s="11" t="n">
+      <c r="I14" s="12" t="n">
         <f aca="false">IFERROR(H14/F14,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="10" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="11" t="n">
         <f aca="false">IF(G15="Vinta",(E15*F15)-F15,IF(G15="Persa",-F15,0))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="I15" s="12" t="n">
         <f aca="false">IFERROR(H15/F15,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="10" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="11" t="n">
         <f aca="false">IF(G16="Vinta",(E16*F16)-F16,IF(G16="Persa",-F16,0))</f>
         <v>0</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="12" t="n">
         <f aca="false">IFERROR(H16/F16,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="10" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="11" t="n">
         <f aca="false">IF(G17="Vinta",(E17*F17)-F17,IF(G17="Persa",-F17,0))</f>
         <v>0</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <f aca="false">IFERROR(H17/F17,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="10" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="11" t="n">
         <f aca="false">IF(G18="Vinta",(E18*F18)-F18,IF(G18="Persa",-F18,0))</f>
         <v>0</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="12" t="n">
         <f aca="false">IFERROR(H18/F18,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="10" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="11" t="n">
         <f aca="false">IF(G19="Vinta",(E19*F19)-F19,IF(G19="Persa",-F19,0))</f>
         <v>0</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" s="12" t="n">
         <f aca="false">IFERROR(H19/F19,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="10" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="11" t="n">
         <f aca="false">IF(G20="Vinta",(E20*F20)-F20,IF(G20="Persa",-F20,0))</f>
         <v>0</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" s="12" t="n">
         <f aca="false">IFERROR(H20/F20,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="10" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="11" t="n">
         <f aca="false">IF(G21="Vinta",(E21*F21)-F21,IF(G21="Persa",-F21,0))</f>
         <v>0</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="12" t="n">
         <f aca="false">IFERROR(H21/F21,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="10" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="11" t="n">
         <f aca="false">IF(G22="Vinta",(E22*F22)-F22,IF(G22="Persa",-F22,0))</f>
         <v>0</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="12" t="n">
         <f aca="false">IFERROR(H22/F22,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="10" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="11" t="n">
         <f aca="false">IF(G23="Vinta",(E23*F23)-F23,IF(G23="Persa",-F23,0))</f>
         <v>0</v>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="I23" s="12" t="n">
         <f aca="false">IFERROR(H23/F23,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="10" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="11" t="n">
         <f aca="false">IF(G24="Vinta",(E24*F24)-F24,IF(G24="Persa",-F24,0))</f>
         <v>0</v>
       </c>
-      <c r="I24" s="11" t="n">
+      <c r="I24" s="12" t="n">
         <f aca="false">IFERROR(H24/F24,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="10" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="11" t="n">
         <f aca="false">IF(G25="Vinta",(E25*F25)-F25,IF(G25="Persa",-F25,0))</f>
         <v>0</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="I25" s="12" t="n">
         <f aca="false">IFERROR(H25/F25,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="10" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="11" t="n">
         <f aca="false">IF(G26="Vinta",(E26*F26)-F26,IF(G26="Persa",-F26,0))</f>
         <v>0</v>
       </c>
-      <c r="I26" s="11" t="n">
+      <c r="I26" s="12" t="n">
         <f aca="false">IFERROR(H26/F26,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="10" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="11" t="n">
         <f aca="false">IF(G27="Vinta",(E27*F27)-F27,IF(G27="Persa",-F27,0))</f>
         <v>0</v>
       </c>
-      <c r="I27" s="11" t="n">
+      <c r="I27" s="12" t="n">
         <f aca="false">IFERROR(H27/F27,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="10" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="11" t="n">
         <f aca="false">IF(G28="Vinta",(E28*F28)-F28,IF(G28="Persa",-F28,0))</f>
         <v>0</v>
       </c>
-      <c r="I28" s="11" t="n">
+      <c r="I28" s="12" t="n">
         <f aca="false">IFERROR(H28/F28,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="10" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="11" t="n">
         <f aca="false">IF(G29="Vinta",(E29*F29)-F29,IF(G29="Persa",-F29,0))</f>
         <v>0</v>
       </c>
-      <c r="I29" s="11" t="n">
+      <c r="I29" s="12" t="n">
         <f aca="false">IFERROR(H29/F29,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="10" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="11" t="n">
         <f aca="false">IF(G30="Vinta",(E30*F30)-F30,IF(G30="Persa",-F30,0))</f>
         <v>0</v>
       </c>
-      <c r="I30" s="11" t="n">
+      <c r="I30" s="12" t="n">
         <f aca="false">IFERROR(H30/F30,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="10" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="11" t="n">
         <f aca="false">IF(G31="Vinta",(E31*F31)-F31,IF(G31="Persa",-F31,0))</f>
         <v>0</v>
       </c>
-      <c r="I31" s="11" t="n">
+      <c r="I31" s="12" t="n">
         <f aca="false">IFERROR(H31/F31,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1249,76 +1313,76 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <f aca="false">COUNTA(Scommesse!G2:G31)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <f aca="false">COUNTIF(Scommesse!G2:G31,"Vinta")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <f aca="false">COUNTIF(Scommesse!G2:G31,"Persa")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <f aca="false">IFERROR(B4/B3,0)</f>
         <v>0.666666666666667</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="20" t="n">
         <f aca="false">SUM(Scommesse!F2:F31)</f>
         <v>450</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="20" t="n">
         <f aca="false">SUM(Scommesse!H2:H31)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(B8/B7,0)</f>
         <v>0.0333333333333333</v>
       </c>
@@ -1335,4 +1399,206 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="25"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="25"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="25"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="25"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="25"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="25"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="25"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="25"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="25"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="25"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="25"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="25"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="25"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="25"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="70" count="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="73" count="73">
   <si>
     <t>Campo</t>
   </si>
@@ -234,6 +234,17 @@
   </si>
   <si>
     <t>https://t.me/doubleuptip</t>
+  </si>
+  <si>
+    <t>Mi chiamo Valerio e seguo NFL e calcio da più di 20 anni. Ho aperto questo spazio per tenere traccia delle mie giocate in modo trasparente: ogni riga che leggi qui è una scommessa che ho fatto con i miei soldi, vinta o persa che sia.
+Non vivo di questo e non pretendo di avere un metodo infallibile. Registro tutto perché i numeri scritti sono l'unico modo per non raccontarsela: la memoria tiene le vincite e cancella il resto.
+Quello che trovi nelle note sono le riflessioni che mi porto dietro dopo ogni giornata — soprattutto dagli errori, che sono la parte più utile.</t>
+  </si>
+  <si>
+    <t>Se hai domande o vuoi segnalarmi un errore nei conti, scrivimi a doubleuptip@gmail.com</t>
+  </si>
+  <si>
+    <t>@pocoto11</t>
   </si>
 </sst>
 </file>
@@ -299,7 +310,7 @@
       <name val="Calibri"/>
       <u/>
       <sz val="11"/>
-      <color indexed="4"/>
+      <color indexed="20"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -725,8 +736,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15.0" zeroHeight="1"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="22.0" style="1"/>
     <col min="2" max="2" customWidth="1" width="95.0" style="1"/>
@@ -761,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="8:8" ht="39.75" customHeight="1">
@@ -785,7 +796,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="8:8" ht="15.0" customHeight="1">
@@ -805,14 +816,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15.0" zeroHeight="1"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="16.0" style="0"/>
     <col min="2" max="2" customWidth="1" width="46.0" style="0"/>
@@ -830,23 +840,19 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="8:8" ht="15.0">
+    <row r="2" spans="8:8" ht="15.7">
       <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="8:8" ht="15.0">
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" spans="8:8" ht="15.7">
       <c r="A3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="C3" s="7"/>
     </row>
     <row r="4" spans="8:8" ht="16.8">
       <c r="A4" s="6" t="s">
@@ -855,9 +861,7 @@
       <c r="B4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="C4" s="7"/>
     </row>
     <row r="6" spans="8:8" ht="15.0">
       <c r="A6" s="9" t="s">
@@ -884,14 +888,13 @@
     <hyperlink ref="B4" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultRowHeight="15.0" zeroHeight="1"/>
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="12.0" style="1"/>
     <col min="2" max="2" customWidth="1" width="10.0" style="1"/>
@@ -1507,14 +1510,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15.0" zeroHeight="1"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="32.0" style="1"/>
     <col min="2" max="2" customWidth="1" width="18.0" style="1"/>
@@ -1595,14 +1597,13 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="15.0" zeroHeight="1"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="14.0" style="1"/>
     <col min="2" max="2" customWidth="1" width="38.0" style="1"/>
@@ -1789,6 +1790,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>